--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261022.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261022.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>202611WTEX6F</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>592,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>202611WTEX6F</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>592,000</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,387,000</t>
+          <t>959,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>959,659</t>
+          <t>3,387,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>7,343,249</t>
+          <t>149,386</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>149,386</t>
+          <t>7,343,249</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,244,107</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>2,244,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,214,076</t>
+          <t>509,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>509,000</t>
+          <t>1,214,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>202611WVHFX6F</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>233,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>233,000</t>
+          <t>795,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202611WVHFX6F</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>5,080,956</t>
+          <t>297,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>297,000</t>
+          <t>5,080,956</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,757,640</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>1,757,640</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>1,156,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,156,121</t>
+          <t>1,800,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>425,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>425,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>66,538</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>66,538</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
